--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
   <si>
     <t>Filename</t>
   </si>
@@ -811,673 +811,679 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9852,0.0018,0.0029,0.0016</t>
-  </si>
-  <si>
-    <t>0.0004,0.0049,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0591,0.0003,0.0000,0.9798</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9886,0.0027,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0269,0.0000,0.9966</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0585,0.0002,0.0000,0.9853</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
     <t>0.9996,0.0003,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9986,0.0010,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9744,0.0005,0.0250,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0010,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.6196,0.0006,0.4964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.9917,0.0003,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0084,0.9900,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9417,0.0004,0.0620,0.0002</t>
+  </si>
+  <si>
+    <t>0.1712,0.0004,0.8839,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.9937,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0793,0.9322,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9836,0.0094,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9996,0.0011</t>
+  </si>
+  <si>
+    <t>0.0055,0.9603,0.0800,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9692,0.0035,0.0167,0.0005</t>
+  </si>
+  <si>
+    <t>0.3339,0.7143,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.9985,0.0042,0.0000</t>
+  </si>
+  <si>
+    <t>0.0149,0.9162,0.0151,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0104,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0000,0.9440,0.0163</t>
+  </si>
+  <si>
+    <t>0.0000,0.0595,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9983,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.8677,0.0323,0.6971</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.5186,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0065,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0018,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.0047,0.9883,0.0030</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0017,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.0025,0.9986,0.0008</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9973,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0038,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.9989,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0064,0.9930,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9898,0.0001,0.0076,0.0001</t>
+  </si>
+  <si>
+    <t>0.9765,0.0090,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.0003,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9790,0.9358,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.8089,0.9758,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0072,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.9903,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.0006,0.9992</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.0011,0.9997</t>
+  </si>
+  <si>
+    <t>0.0008,0.0000,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0355,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9734,0.9718,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9801,0.4231,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.8666,0.9824,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9817,0.9715,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.0020,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0037,0.9930,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0919,0.9136,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.8302,0.0099,0.0900,0.0010</t>
+  </si>
+  <si>
+    <t>0.4191,0.0082,0.3454,0.0052</t>
+  </si>
+  <si>
+    <t>0.5288,0.0011,0.3492,0.0053</t>
+  </si>
+  <si>
+    <t>0.3943,0.0012,0.5856,0.0014</t>
+  </si>
+  <si>
+    <t>0.0005,0.1359,0.0012,0.9437</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9888,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9264,0.0480,0.0071,0.0004</t>
+  </si>
+  <si>
+    <t>0.9477,0.0530,0.0013,0.0002</t>
+  </si>
+  <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9651,0.0017,0.0231,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.0007,0.9941,0.0011</t>
-  </si>
-  <si>
-    <t>0.5118,0.0002,0.6616,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.0002,0.9956,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.9929,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.7461,0.0004,0.3172,0.0003</t>
-  </si>
-  <si>
-    <t>0.5200,0.0013,0.5902,0.0004</t>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9808,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.2662,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.1592,0.0005,0.9071,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.3829,0.0040,0.5598,0.0017</t>
+  </si>
+  <si>
+    <t>0.0848,0.0000,0.9571,0.0001</t>
+  </si>
+  <si>
+    <t>0.0763,0.0372,0.8551,0.0004</t>
+  </si>
+  <si>
+    <t>0.0225,0.0002,0.0063,0.9858</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0003,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9949,0.6142,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0013,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0585,0.9342,0.0023,0.0175</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.2574,0.8062,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.1936,0.0003,0.0004,0.8670</t>
+  </si>
+  <si>
+    <t>0.0007,0.0053,0.9979,0.0027</t>
+  </si>
+  <si>
+    <t>0.6059,0.0000,0.0050,0.2515</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0267,0.9742,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1612,0.8602,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9288,0.0538,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9313,0.0409,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9891,0.0087,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9668,0.0464,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7309,0.0411,0.1235,0.0012</t>
+  </si>
+  <si>
+    <t>0.9366,0.0895,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0025,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9897,0.0079,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0052,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9709,0.0038,0.0168,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0115,0.9956,0.0011</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0039,0.9999,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0005,0.0004,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.3700,0.6187,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.8725,0.0595,0.0261,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0007</t>
-  </si>
-  <si>
-    <t>0.0044,0.7850,0.5171,0.0001</t>
-  </si>
-  <si>
-    <t>0.9747,0.0108,0.0043,0.0007</t>
-  </si>
-  <si>
-    <t>0.9862,0.0025,0.0048,0.0003</t>
-  </si>
-  <si>
-    <t>0.3746,0.6969,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9961,0.3981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0348,0.0230,0.6532,0.0295</t>
-  </si>
-  <si>
-    <t>0.0006,0.0033,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0125,0.0000,0.8326,0.0081</t>
-  </si>
-  <si>
-    <t>0.0000,0.0069,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0080,0.7656,0.0330,0.6288</t>
-  </si>
-  <si>
-    <t>0.0003,0.9981,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9972,0.0227,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0010,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0222,0.9968,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.0013,0.9975,0.0016</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0022,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0037,0.0450,0.9810,0.0010</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0013,0.9993,0.0015</t>
+    <t>0.0000,0.0005,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0007,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0005,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.5602,0.0018,0.4560,0.0004</t>
+  </si>
+  <si>
+    <t>0.0060,0.0015,0.9911,0.0001</t>
+  </si>
+  <si>
+    <t>0.0692,0.0213,0.8728,0.0006</t>
+  </si>
+  <si>
+    <t>0.8176,0.0104,0.1370,0.0003</t>
+  </si>
+  <si>
+    <t>0.9324,0.0005,0.0650,0.0002</t>
+  </si>
+  <si>
+    <t>0.8175,0.0108,0.1015,0.0005</t>
+  </si>
+  <si>
+    <t>0.4496,0.7352,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.9989,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9805,0.0287,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9117,0.0935,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.0603,0.9540,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.6454,0.1309,0.0044,0.0013</t>
+  </si>
+  <si>
+    <t>0.9944,0.0001,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.9365,0.0008,0.0307,0.0026</t>
+  </si>
+  <si>
+    <t>0.9266,0.0083,0.0441,0.0005</t>
+  </si>
+  <si>
+    <t>0.9431,0.0052,0.0320,0.0005</t>
+  </si>
+  <si>
+    <t>0.0031,0.0003,0.9963,0.0003</t>
+  </si>
+  <si>
+    <t>0.0209,0.0056,0.9495,0.0023</t>
+  </si>
+  <si>
+    <t>0.0028,0.0021,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.0002,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0033,0.0251,0.9795,0.0015</t>
   </si>
   <si>
     <t>0.9993,0.0002,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9974,0.0018,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9660,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0009,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0020,0.9968,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0069,0.9924,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0002,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.3923,0.0067,0.5131,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0010,0.9997,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9879,0.9773,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.8156,0.8228,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0933,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9482,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.0015,0.9993</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0015,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9855,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9369,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9711,0.8673,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.1880,0.9848,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9881,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9863,0.7521,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
+    <t>0.9939,0.0046,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9917,0.0115,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0014,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0016,0.9990,0.0008</t>
+  </si>
+  <si>
+    <t>0.0862,0.0051,0.8917,0.0016</t>
+  </si>
+  <si>
+    <t>0.8478,0.0003,0.0646,0.0064</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.1497,0.9875,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0021,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.0002,0.9951,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0034,0.9990,0.0003</t>
+  </si>
+  <si>
+    <t>0.9930,0.0001,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.9356,0.0001,0.1016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0002,0.0002</t>
   </si>
   <si>
     <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0026,0.0009,0.9966,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9985,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9981,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1025,0.9147,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.9722,0.0033,0.0068,0.0007</t>
-  </si>
-  <si>
-    <t>0.7654,0.0025,0.1683,0.0010</t>
-  </si>
-  <si>
-    <t>0.9680,0.0065,0.0076,0.0005</t>
-  </si>
-  <si>
-    <t>0.0329,0.0039,0.9552,0.0020</t>
-  </si>
-  <si>
-    <t>0.0017,0.9473,0.0080,0.3609</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9907,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9989,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.5089,0.5654,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8779,0.1365,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.2449,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3924,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.1514,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9793,0.0013,0.0124,0.0003</t>
-  </si>
-  <si>
-    <t>0.0139,0.0000,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.1317,0.0124,0.8163,0.0018</t>
-  </si>
-  <si>
-    <t>0.0027,0.0000,0.0002,0.9989</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9324,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0186,0.9779,0.0007,0.0096</t>
-  </si>
-  <si>
-    <t>0.7999,0.2118,0.0031,0.0016</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0212,0.0001,0.0000,0.9952</t>
-  </si>
-  <si>
-    <t>0.0001,0.0019,0.9996,0.0040</t>
-  </si>
-  <si>
-    <t>0.9556,0.0000,0.0013,0.0228</t>
-  </si>
-  <si>
-    <t>0.9978,0.0003,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.0304,0.9717,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4147,0.5967,0.0037,0.0007</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.5686,0.3577,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9779,0.0207,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.1262,0.9070,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.2750,0.1382,0.3551,0.0005</t>
-  </si>
-  <si>
-    <t>0.9955,0.0043,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0016,0.0032,0.0007</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0026,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0019,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9435,0.0173,0.0160,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0025,0.9981,0.0007</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.9982,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0028,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0044,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0191,0.0060,0.9687,0.0011</t>
-  </si>
-  <si>
-    <t>0.0022,0.0007,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.0075,0.0057,0.9862,0.0003</t>
-  </si>
-  <si>
-    <t>0.0075,0.0084,0.9819,0.0002</t>
-  </si>
-  <si>
-    <t>0.0255,0.0202,0.9349,0.0003</t>
-  </si>
-  <si>
-    <t>0.6209,0.0078,0.3927,0.0002</t>
-  </si>
-  <si>
-    <t>0.5113,0.0017,0.4603,0.0009</t>
-  </si>
-  <si>
-    <t>0.1168,0.0184,0.8280,0.0001</t>
-  </si>
-  <si>
-    <t>0.0134,0.9910,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9985,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9398,0.0943,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0021,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.0572,0.9573,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.5589,0.0615,0.0424,0.0023</t>
-  </si>
-  <si>
-    <t>0.9942,0.0002,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9658,0.0065,0.0044,0.0009</t>
-  </si>
-  <si>
-    <t>0.9236,0.0111,0.0350,0.0014</t>
-  </si>
-  <si>
-    <t>0.7924,0.0007,0.1590,0.0020</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0004</t>
-  </si>
-  <si>
-    <t>0.0050,0.0038,0.9824,0.0018</t>
-  </si>
-  <si>
-    <t>0.0002,0.0017,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0004,0.9967,0.0002</t>
-  </si>
-  <si>
-    <t>0.0026,0.0037,0.9843,0.0040</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9960,0.0023,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9989,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0029,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.0013,0.0007,0.9984,0.0002</t>
-  </si>
-  <si>
-    <t>0.0355,0.1211,0.8264,0.0007</t>
-  </si>
-  <si>
-    <t>0.9909,0.0002,0.0035,0.0006</t>
-  </si>
-  <si>
-    <t>0.0076,0.0002,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.1671,0.9915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0005,0.9953,0.0002</t>
-  </si>
-  <si>
-    <t>0.0041,0.0009,0.9940,0.0009</t>
-  </si>
-  <si>
-    <t>0.0019,0.0028,0.9927,0.0028</t>
-  </si>
-  <si>
-    <t>0.9864,0.0005,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.9635,0.0001,0.0470,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0010,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0020,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0036,0.9918,0.0040</t>
-  </si>
-  <si>
-    <t>0.0002,0.0194,0.9985,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0040,0.0005,0.9921,0.0034</t>
-  </si>
-  <si>
-    <t>0.0003,0.0022,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.0001,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.9848,0.0006,0.0002,0.0098</t>
-  </si>
-  <si>
-    <t>0.0010,0.0177,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.0022,0.0000,0.0001,0.9993</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9747,0.0020,0.0068,0.0040</t>
+    <t>0.9987,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0036,0.0081,0.9880,0.0026</t>
+  </si>
+  <si>
+    <t>0.0003,0.0112,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0109,0.9853,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.1261,0.0009,0.8458,0.0078</t>
+  </si>
+  <si>
+    <t>0.0005,0.0046,0.9982,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9990,0.0014</t>
+  </si>
+  <si>
+    <t>0.9957,0.0004,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.0379,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0555,0.0003,0.0001,0.9838</t>
+  </si>
+  <si>
+    <t>0.9586,0.0027,0.0084,0.0078</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1869,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1877,7 +1883,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1891,7 +1897,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1905,7 +1911,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1919,7 +1925,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1933,7 +1939,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1947,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1961,7 +1967,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1975,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1989,7 +1995,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2003,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2017,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2031,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2045,7 +2051,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2056,10 +2062,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2073,7 +2079,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2087,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2101,7 +2107,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2115,7 +2121,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2129,7 +2135,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2143,7 +2149,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2157,7 +2163,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2171,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,7 +2191,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2199,7 +2205,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2213,7 +2219,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2227,7 +2233,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2241,7 +2247,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2255,7 +2261,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,7 +2275,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2283,7 +2289,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2297,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2308,10 +2314,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2325,7 +2331,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2339,7 +2345,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2353,7 +2359,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2367,7 +2373,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2378,10 +2384,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2395,7 +2401,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2409,7 +2415,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2423,7 +2429,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2437,7 +2443,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2451,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2465,7 +2471,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2479,7 +2485,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2493,7 +2499,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2504,10 +2510,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2521,7 +2527,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2535,7 +2541,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2549,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2563,7 +2569,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2577,7 +2583,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2591,7 +2597,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2605,7 +2611,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2619,7 +2625,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2633,7 +2639,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2647,7 +2653,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2661,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2675,7 +2681,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2689,7 +2695,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2703,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2717,7 +2723,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2731,7 +2737,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2745,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2759,7 +2765,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2773,7 +2779,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2787,7 +2793,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2801,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2815,7 +2821,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2826,10 +2832,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2843,7 +2849,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2857,7 +2863,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2871,7 +2877,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2885,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2899,7 +2905,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2913,7 +2919,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2927,7 +2933,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2941,7 +2947,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2955,7 +2961,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2969,7 +2975,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2983,7 +2989,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2994,10 +3000,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3011,7 +3017,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3022,10 +3028,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3036,10 +3042,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3053,7 +3059,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3067,7 +3073,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3081,7 +3087,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>345</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3095,7 +3101,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3109,7 +3115,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3123,7 +3129,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3137,7 +3143,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3151,7 +3157,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3165,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3179,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3193,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3207,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>272</v>
+        <v>352</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3221,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3235,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>353</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3249,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3263,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>353</v>
+        <v>273</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3291,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3417,7 +3423,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3470,7 +3476,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D117" t="s">
         <v>366</v>
@@ -3512,7 +3518,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>369</v>
@@ -3543,7 +3549,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3557,7 +3563,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3571,7 +3577,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3585,7 +3591,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3596,10 +3602,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3613,7 +3619,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3627,7 +3633,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3641,7 +3647,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>269</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3683,7 +3689,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>379</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3697,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3711,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3725,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3736,10 +3742,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3753,7 +3759,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3767,7 +3773,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3781,7 +3787,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3795,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3806,10 +3812,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3823,7 +3829,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3837,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3851,7 +3857,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3865,7 +3871,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3879,7 +3885,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3893,7 +3899,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3907,7 +3913,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3921,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3935,7 +3941,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3949,7 +3955,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>397</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3960,10 +3966,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3977,7 +3983,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3991,7 +3997,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4005,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4019,7 +4025,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4033,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4047,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4061,7 +4067,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4075,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4089,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4103,7 +4109,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4117,7 +4123,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4131,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4145,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>407</v>
+        <v>354</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4159,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>352</v>
+        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4173,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4187,7 +4193,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4201,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4215,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4229,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>377</v>
+        <v>273</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4243,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4257,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4271,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4282,10 +4288,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4299,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4313,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4327,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4341,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4355,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4369,7 +4375,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4383,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4397,7 +4403,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4411,7 +4417,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4425,7 +4431,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4439,7 +4445,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4453,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4467,7 +4473,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4481,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4495,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4509,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4520,10 +4526,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4537,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4551,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4565,7 +4571,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4579,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4590,10 +4596,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4607,7 +4613,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4621,7 +4627,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4635,7 +4641,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4649,7 +4655,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4663,7 +4669,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4677,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4691,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4705,7 +4711,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4719,7 +4725,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4733,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4747,7 +4753,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4761,7 +4767,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4775,7 +4781,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4789,7 +4795,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4803,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4817,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>452</v>
+        <v>353</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4831,7 +4837,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4845,7 +4851,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4859,7 +4865,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>410</v>
+        <v>456</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4873,7 +4879,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4887,7 +4893,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4901,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4915,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>410</v>
+        <v>460</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4929,7 +4935,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4943,7 +4949,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4957,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4971,7 +4977,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4985,7 +4991,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4999,7 +5005,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5013,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>324</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5027,7 +5033,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5041,7 +5047,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>422</v>
+        <v>328</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5055,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5069,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5083,7 +5089,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5097,7 +5103,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5111,7 +5117,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5125,7 +5131,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5139,7 +5145,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>345</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5153,7 +5159,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>471</v>
+        <v>274</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5167,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5181,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5195,7 +5201,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>271</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5209,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>473</v>
+        <v>376</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5223,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5237,7 +5243,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5251,7 +5257,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,7 +5271,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>477</v>
+        <v>314</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5279,7 +5285,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5293,7 +5299,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5307,7 +5313,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5335,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5349,7 +5355,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5363,7 +5369,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5377,7 +5383,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5391,7 +5397,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5405,7 +5411,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>486</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5419,7 +5425,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
